--- a/ISOC_result/Living_room_11/Living_room_11_result.xlsx
+++ b/ISOC_result/Living_room_11/Living_room_11_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ISOC\ISOC_result\Living_room_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B3D3A5-69D3-4172-A989-11B86D25DCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDFF446-D5F0-4E8F-A6CB-E60C78CF0BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8F062009-FD71-4F10-8C79-40340D4D7484}"/>
   </bookViews>
@@ -146,13 +146,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -534,14 +534,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -664,22 +664,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>0</v>
       </c>
-      <c r="B8" s="11">
-        <v>11</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="9">
+        <v>11</v>
+      </c>
+      <c r="C8" s="9">
         <v>5945.51</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>410.3</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>57124</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <v>94.75</v>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>2</v>
       </c>
-      <c r="B10" s="11">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="9">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9">
         <v>5792.67</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>282.38</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>56872</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>94.33</v>
       </c>
     </row>
@@ -754,7 +754,7 @@
         <v>6331.48</v>
       </c>
       <c r="D12" s="2">
-        <v>715.72</v>
+        <v>524.13</v>
       </c>
       <c r="E12" s="2">
         <v>57342</v>
@@ -834,7 +834,7 @@
         <v>6469.97</v>
       </c>
       <c r="D16" s="2">
-        <v>926.8</v>
+        <v>792.23</v>
       </c>
       <c r="E16" s="2">
         <v>57522</v>
@@ -1254,7 +1254,7 @@
         <v>5899.03</v>
       </c>
       <c r="D37" s="2">
-        <v>1042.23</v>
+        <v>329.57</v>
       </c>
       <c r="E37" s="2">
         <v>56302</v>
@@ -1314,7 +1314,7 @@
         <v>6332.65</v>
       </c>
       <c r="D40" s="4">
-        <v>703.93</v>
+        <v>638.73</v>
       </c>
       <c r="E40" s="4">
         <v>56167</v>
@@ -1394,7 +1394,7 @@
         <v>6449.49</v>
       </c>
       <c r="D44" s="2">
-        <v>738.91</v>
+        <v>396.72</v>
       </c>
       <c r="E44" s="2">
         <v>56512</v>
